--- a/data/marketlogins.xlsx
+++ b/data/marketlogins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBS NL62\PycharmProjects\PythonProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C17558-FD6A-4395-84D3-31999F4A64E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E29D8E-414C-4117-8E21-653A9B8446F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B868D1A5-722E-4BB5-857C-FD1FB6EABAD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{B868D1A5-722E-4BB5-857C-FD1FB6EABAD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="46">
   <si>
     <t>Waco</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Market</t>
+  </si>
+  <si>
+    <t>Purelywireless@8</t>
   </si>
 </sst>
 </file>
@@ -549,7 +552,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,7 +574,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,7 +607,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -615,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -626,7 +629,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -637,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -761,6 +764,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -861,7 +865,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
